--- a/data/gas_rates_weekdays_converted_to_kwh_202607.xlsx
+++ b/data/gas_rates_weekdays_converted_to_kwh_202607.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/syoungy/Library/CloudStorage/GoogleDrive-amybackup0923@gmail.com/My Drive/Back Up Drive/Research/1. Working/[1.Intermediate] Heat pump installer/5-1. calculation/data2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/syoungy/Library/CloudStorage/GoogleDrive-amybackup0923@gmail.com/My Drive/Back Up Drive/Research/1. Working/[1.Intermediate] Heat pump installer/5-1. calculation/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91A3D0A9-C028-DA4C-8BE2-E9C65039EA30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA3B329-A2B8-9B43-BC56-78D8E1628D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{447DBB6F-F31E-B64F-92E3-A80505AD8660}"/>
   </bookViews>
@@ -647,76 +647,100 @@
         <v>30</v>
       </c>
       <c r="E2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f>0.95/29.3</f>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="F2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" ref="F2:AB2" si="0">0.95/29.3</f>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="G2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="H2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="I2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="J2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="K2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="L2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="M2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="N2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="O2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="P2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="Q2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="R2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="S2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="T2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="U2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="V2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="W2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="X2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="Y2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="Z2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="AA2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
       <c r="AB2" s="3">
-        <v>3.1450511945392487E-2</v>
+        <f t="shared" si="0"/>
+        <v>3.2423208191126277E-2</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="17" x14ac:dyDescent="0.2">
